--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
   </si>
 </sst>
 </file>
@@ -562,16 +571,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.18000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +597,19 @@
         <v>27</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>27</v>
       </c>
-      <c r="E3">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -650,16 +665,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>94.87</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,7 +700,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +740,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,10 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>MENA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -710,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,16 +751,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920105</v>
+        <v>21330051920109</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -761,6 +770,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
@@ -489,10 +489,10 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>37</v>
@@ -501,7 +501,7 @@
         <v>94.87</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -580,10 +580,10 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -592,7 +592,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -671,10 +671,10 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -683,7 +683,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,25 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>MENA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -719,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,10 +766,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -774,16 +783,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920105</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -792,6 +801,29 @@
         <v>10</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,28 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>MENA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -683,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -718,7 +700,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -760,16 +742,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920109</v>
+        <v>21330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -778,52 +760,6 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920260</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920105</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>
